--- a/ARQUIVOS_GERADOS/BI_ABASTECIMENTO/OS_GERAL.xlsx
+++ b/ARQUIVOS_GERADOS/BI_ABASTECIMENTO/OS_GERAL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,19 +477,19 @@
         <v>46133</v>
       </c>
       <c r="B3" t="n">
-        <v>1574</v>
+        <v>2320</v>
       </c>
       <c r="C3" t="n">
-        <v>356</v>
+        <v>680</v>
       </c>
       <c r="D3" t="n">
         <v>434</v>
       </c>
       <c r="E3" t="n">
-        <v>784</v>
+        <v>1206</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4">
@@ -497,18 +497,38 @@
         <v>46134</v>
       </c>
       <c r="B4" t="n">
-        <v>1182</v>
+        <v>2458</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>585</v>
       </c>
       <c r="D4" t="n">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="E4" t="n">
-        <v>597</v>
+        <v>1275</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1279</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>632</v>
+      </c>
+      <c r="E5" t="n">
+        <v>647</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
